--- a/NingshaRace/Docs/开发需求/凝砂需求表.xlsx
+++ b/NingshaRace/Docs/开发需求/凝砂需求表.xlsx
@@ -2388,7 +2388,11 @@
       <c r="A3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="14"/>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="C3" s="14"/>
       <c r="D3" s="14"/>
       <c r="E3" s="14"/>
@@ -2410,7 +2414,11 @@
       <c r="A4" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="14"/>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="C4" s="14" t="s">
         <v>6</v>
       </c>
@@ -2434,7 +2442,11 @@
       <c r="A5" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="14"/>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="C5" s="14" t="s">
         <v>8</v>
       </c>
@@ -2458,7 +2470,11 @@
       <c r="A6" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="14"/>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="C6" s="14" t="s">
         <v>10</v>
       </c>
@@ -2482,7 +2498,11 @@
       <c r="A7" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="14"/>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="C7" s="14" t="s">
         <v>12</v>
       </c>
@@ -2506,7 +2526,11 @@
       <c r="A8" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="14"/>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="C8" s="14" t="s">
         <v>14</v>
       </c>
@@ -2530,7 +2554,11 @@
       <c r="A9" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="14"/>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="C9" s="14" t="s">
         <v>15</v>
       </c>
@@ -2554,7 +2582,11 @@
       <c r="A10" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="14"/>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="C10" s="14" t="s">
         <v>17</v>
       </c>
@@ -2578,7 +2610,11 @@
       <c r="A11" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="14"/>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="C11" s="14" t="s">
         <v>19</v>
       </c>
@@ -2602,7 +2638,11 @@
       <c r="A12" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="14"/>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="C12" s="14" t="s">
         <v>21</v>
       </c>
@@ -2626,7 +2666,11 @@
       <c r="A13" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="14"/>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="C13" s="14" t="s">
         <v>23</v>
       </c>
@@ -2650,7 +2694,11 @@
       <c r="A14" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="14"/>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="C14" s="14" t="s">
         <v>24</v>
       </c>
@@ -2674,7 +2722,11 @@
       <c r="A15" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="14"/>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="C15" s="14" t="s">
         <v>25</v>
       </c>
@@ -2698,7 +2750,11 @@
       <c r="A16" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="14"/>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="C16" s="14" t="s">
         <v>26</v>
       </c>
@@ -2722,7 +2778,11 @@
       <c r="A17" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="14"/>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="C17" s="14" t="s">
         <v>28</v>
       </c>
@@ -2746,7 +2806,11 @@
       <c r="A18" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="14"/>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="C18" s="14" t="s">
         <v>30</v>
       </c>
@@ -2770,7 +2834,11 @@
       <c r="A19" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="14"/>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="C19" s="14" t="s">
         <v>31</v>
       </c>
@@ -6724,7 +6792,7 @@
       <c r="S2" s="9"/>
       <c r="T2" s="9"/>
     </row>
-    <row r="3" ht="51.75" spans="1:20">
+    <row r="3" ht="118" spans="1:20" customHeight="1">
       <c r="A3" s="10" t="s">
         <v>70</v>
       </c>
@@ -6737,8 +6805,11 @@
         <v>72</v>
       </c>
       <c r="F3" s="10"/>
-      <c r="G3" s="10" t="s">
-        <v>73</v>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">这是一条说明，并非实际任务要求
+2026-10-31：✓ 表示 1.7 代码已实现；不兼容旧蚁群存档，1.6 与独立蚁狮不在范围。AI贴图占位不代表正式美术完成。所有路径相对模组根目录。</t>
+        </is>
       </c>
       <c r="H3" s="10"/>
       <c r="I3" s="10"/>
@@ -6754,12 +6825,16 @@
       <c r="S3" s="10"/>
       <c r="T3" s="10"/>
     </row>
-    <row r="4" s="6" customFormat="1" ht="34.5" spans="1:20">
+    <row r="4" s="6" customFormat="1" ht="100" spans="1:20" customHeight="1">
       <c r="A4" s="11" t="s">
         <v>74</v>
       </c>
       <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D4" s="11" t="s">
         <v>75</v>
       </c>
@@ -6767,7 +6842,11 @@
         <v>76</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每巢独立组件 → 每图一个管理组件、每巢独立状态和阵营 → 减少组件开销；巢毁释放内部成员、清任务并转为猎杀人类。三场景统一入口，祭坛固定等级，墓葬保留规模/休眠且不添贵重品。</t>
+        </is>
+      </c>
       <c r="H4" s="11"/>
       <c r="I4" s="11"/>
       <c r="J4" s="11"/>
@@ -6782,12 +6861,16 @@
       <c r="S4" s="11"/>
       <c r="T4" s="11"/>
     </row>
-    <row r="5" ht="34.5" spans="1:20">
+    <row r="5" ht="64" spans="1:20" customHeight="1">
       <c r="A5" s="10" t="s">
         <v>74</v>
       </c>
       <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D5" s="10" t="s">
         <v>77</v>
       </c>
@@ -6795,7 +6878,11 @@
         <v>78</v>
       </c>
       <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">跨图按巢序号复用阵营 → 每巢创建唯一隐藏永久敌对阵营 → 避免跨图混巢；其他要求不变。</t>
+        </is>
+      </c>
       <c r="H5" s="10"/>
       <c r="I5" s="10"/>
       <c r="J5" s="10"/>
@@ -6810,12 +6897,16 @@
       <c r="S5" s="10"/>
       <c r="T5" s="10"/>
     </row>
-    <row r="6" s="6" customFormat="1" ht="34.5" spans="1:20">
+    <row r="6" s="6" customFormat="1" ht="64" spans="1:20" customHeight="1">
       <c r="A6" s="11" t="s">
         <v>74</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D6" s="11" t="s">
         <v>79</v>
       </c>
@@ -6823,7 +6914,11 @@
         <v>80</v>
       </c>
       <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">成员信息按需求实现；蚁后独立引用，休眠爆浆蚁仍计入上限；生成、死亡事件更新。</t>
+        </is>
+      </c>
       <c r="H6" s="11"/>
       <c r="I6" s="11"/>
       <c r="J6" s="11"/>
@@ -6838,12 +6933,16 @@
       <c r="S6" s="11"/>
       <c r="T6" s="11"/>
     </row>
-    <row r="7" ht="34.5" spans="1:20">
+    <row r="7" ht="64" spans="1:20" customHeight="1">
       <c r="A7" s="10" t="s">
         <v>74</v>
       </c>
       <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D7" s="10" t="s">
         <v>81</v>
       </c>
@@ -6851,7 +6950,11 @@
         <v>82</v>
       </c>
       <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">建筑信息按需求实现；建成/损毁事件登记，等级决定上限，损毁释放库存并取消引用它的任务。</t>
+        </is>
+      </c>
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
@@ -6866,12 +6969,16 @@
       <c r="S7" s="10"/>
       <c r="T7" s="10"/>
     </row>
-    <row r="8" s="6" customFormat="1" ht="34.5" spans="1:20">
+    <row r="8" s="6" customFormat="1" ht="64" spans="1:20" customHeight="1">
       <c r="A8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D8" s="11" t="s">
         <v>83</v>
       </c>
@@ -6879,7 +6986,11 @@
         <v>84</v>
       </c>
       <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仅每日统计 → 每日全量统计并在入库/取食/消耗后更新，付款前重读实物且含蜜露塔库存 → 避免过期营养和重复扣款。</t>
+        </is>
+      </c>
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
       <c r="J8" s="11"/>
@@ -6894,12 +7005,16 @@
       <c r="S8" s="11"/>
       <c r="T8" s="11"/>
     </row>
-    <row r="9" ht="34.5" spans="1:20">
+    <row r="9" ht="64" spans="1:20" customHeight="1">
       <c r="A9" s="10" t="s">
         <v>74</v>
       </c>
       <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D9" s="10" t="s">
         <v>85</v>
       </c>
@@ -6907,7 +7022,11 @@
         <v>86</v>
       </c>
       <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">按工蚁&gt;飞镰&gt;兵蚁&gt;破军&gt;吐酸派孵化任务；记录执行者、营养预留、进度，中断/死亡释放。</t>
+        </is>
+      </c>
       <c r="H9" s="10"/>
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
@@ -6922,12 +7041,16 @@
       <c r="S9" s="10"/>
       <c r="T9" s="10"/>
     </row>
-    <row r="10" s="6" customFormat="1" ht="34.5" spans="1:20">
+    <row r="10" s="6" customFormat="1" ht="64" spans="1:20" customHeight="1">
       <c r="A10" s="11" t="s">
         <v>74</v>
       </c>
       <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D10" s="11" t="s">
         <v>87</v>
       </c>
@@ -6935,7 +7058,11 @@
         <v>88</v>
       </c>
       <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">即时建造/修复/升级 → 按表列优先级由工蚁领任务施工，预留原石与营养，缺料跳过并安排搬石 → 统一任务和真实扣料。</t>
+        </is>
+      </c>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
       <c r="J10" s="11"/>
@@ -6950,12 +7077,16 @@
       <c r="S10" s="11"/>
       <c r="T10" s="11"/>
     </row>
-    <row r="11" ht="34.5" spans="1:20">
+    <row r="11" ht="64" spans="1:20" customHeight="1">
       <c r="A11" s="10" t="s">
         <v>74</v>
       </c>
       <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D11" s="10" t="s">
         <v>89</v>
       </c>
@@ -6963,7 +7094,11 @@
         <v>90</v>
       </c>
       <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">按需求保留超过一天口粮、4 个地面食物格和至少一座粮穴；不足两天优先搬食物，扣料先完整规划，孵化另留新成员口粮。</t>
+        </is>
+      </c>
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
@@ -6978,12 +7113,16 @@
       <c r="S11" s="10"/>
       <c r="T11" s="10"/>
     </row>
-    <row r="12" s="6" customFormat="1" spans="1:20">
+    <row r="12" s="6" customFormat="1" spans="1:20" ht="64" customHeight="1">
       <c r="A12" s="11" t="s">
         <v>74</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D12" s="11" t="s">
         <v>91</v>
       </c>
@@ -6991,7 +7130,11 @@
         <v>92</v>
       </c>
       <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">保留热点和伤亡规则，调查增加破军蚁；警报/撤退取消不算失败，全灭也报告结果。</t>
+        </is>
+      </c>
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
       <c r="J12" s="11"/>
@@ -7006,12 +7149,16 @@
       <c r="S12" s="11"/>
       <c r="T12" s="11"/>
     </row>
-    <row r="13" ht="34.5" spans="1:20">
+    <row r="13" ht="64" spans="1:20" customHeight="1">
       <c r="A13" s="10" t="s">
         <v>74</v>
       </c>
       <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D13" s="10" t="s">
         <v>93</v>
       </c>
@@ -7019,7 +7166,11 @@
         <v>94</v>
       </c>
       <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">按需求触发 2500 tick 警报；护卫分守蚁后/蚁巢，蚁后入巢后全部守巢，警报结束释放原 Pawn。</t>
+        </is>
+      </c>
       <c r="H13" s="10"/>
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
@@ -7034,12 +7185,16 @@
       <c r="S13" s="10"/>
       <c r="T13" s="10"/>
     </row>
-    <row r="14" s="6" customFormat="1" spans="1:20">
+    <row r="14" s="6" customFormat="1" spans="1:20" ht="64" customHeight="1">
       <c r="A14" s="11" t="s">
         <v>74</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D14" s="11" t="s">
         <v>95</v>
       </c>
@@ -7047,7 +7202,11 @@
         <v>96</v>
       </c>
       <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">按需求给有额度工蚁安排取蜜露；容器、物资与目的地统一预留，实物转移并刷新营养。</t>
+        </is>
+      </c>
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
       <c r="J14" s="11"/>
@@ -7062,12 +7221,16 @@
       <c r="S14" s="11"/>
       <c r="T14" s="11"/>
     </row>
-    <row r="15" ht="34.5" spans="1:20">
+    <row r="15" ht="64" spans="1:20" customHeight="1">
       <c r="A15" s="10" t="s">
         <v>74</v>
       </c>
       <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D15" s="10" t="s">
         <v>97</v>
       </c>
@@ -7075,7 +7238,11 @@
         <v>98</v>
       </c>
       <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">按 80/160/240 格、食物优先分层；不足两天口粮只搬食物且不限距离；不可达/无容量任务不堵后续任务。</t>
+        </is>
+      </c>
       <c r="H15" s="10"/>
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
@@ -7090,12 +7257,16 @@
       <c r="S15" s="10"/>
       <c r="T15" s="10"/>
     </row>
-    <row r="16" s="6" customFormat="1" ht="51.75" spans="1:20">
+    <row r="16" s="6" customFormat="1" ht="64" spans="1:20" customHeight="1">
       <c r="A16" s="11" t="s">
         <v>74</v>
       </c>
       <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D16" s="11" t="s">
         <v>99</v>
       </c>
@@ -7103,7 +7274,11 @@
         <v>100</v>
       </c>
       <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">返回不足两只 → 包括全灭；三级以上派可行动飞镰/吐酸/破军，往返兵蚁速度，抵达作战 4500 tick → 补齐零返回边界。</t>
+        </is>
+      </c>
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
       <c r="J16" s="11"/>
@@ -7118,12 +7293,16 @@
       <c r="S16" s="11"/>
       <c r="T16" s="11"/>
     </row>
-    <row r="17" spans="1:20">
+    <row r="17" spans="1:20" ht="64" customHeight="1">
       <c r="A17" s="10" t="s">
         <v>74</v>
       </c>
       <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D17" s="10" t="s">
         <v>101</v>
       </c>
@@ -7131,7 +7310,11 @@
         <v>102</v>
       </c>
       <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">保留 10000 tick 内至少 50% 常规成员伤亡、撤退 10000 tick；统计五种普通蚁，不含蚁后/爆浆。</t>
+        </is>
+      </c>
       <c r="H17" s="10"/>
       <c r="I17" s="10"/>
       <c r="J17" s="10"/>
@@ -7146,12 +7329,16 @@
       <c r="S17" s="10"/>
       <c r="T17" s="10"/>
     </row>
-    <row r="18" s="6" customFormat="1" ht="34.5" spans="1:20">
+    <row r="18" s="6" customFormat="1" ht="46" spans="1:20" customHeight="1">
       <c r="A18" s="11" t="s">
         <v>74</v>
       </c>
       <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D18" s="11" t="s">
         <v>103</v>
       </c>
@@ -7159,7 +7346,11 @@
         <v>104</v>
       </c>
       <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">按巢 60 tick 错峰更新；维修/升级仅规划施工任务，实际扣料在施工完成时结算。</t>
+        </is>
+      </c>
       <c r="H18" s="11"/>
       <c r="I18" s="11"/>
       <c r="J18" s="11"/>
@@ -7174,12 +7365,16 @@
       <c r="S18" s="11"/>
       <c r="T18" s="11"/>
     </row>
-    <row r="19" spans="1:20">
+    <row r="19" spans="1:20" ht="46" customHeight="1">
       <c r="A19" s="10" t="s">
         <v>74</v>
       </c>
       <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D19" s="10" t="s">
         <v>105</v>
       </c>
@@ -7187,7 +7382,11 @@
         <v>106</v>
       </c>
       <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全图可搬运物缓存周期改为 300 tick；领取/执行仍核对目标、空间和预留。</t>
+        </is>
+      </c>
       <c r="H19" s="10"/>
       <c r="I19" s="10"/>
       <c r="J19" s="10"/>
@@ -7224,12 +7423,16 @@
       <c r="S20" s="11"/>
       <c r="T20" s="11"/>
     </row>
-    <row r="21" ht="241.5" spans="1:20">
+    <row r="21" ht="241.5" spans="1:20" customHeight="1">
       <c r="A21" s="8" t="s">
         <v>107</v>
       </c>
       <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D21" s="8" t="s">
         <v>108</v>
       </c>
@@ -7237,8 +7440,12 @@
         <v>109</v>
       </c>
       <c r="F21" s="8"/>
-      <c r="G21" s="8" t="s">
-        <v>110</v>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暂无贴图可用任意原版贴图暂时占位
+50 任意石材 → 3 个可混用原石块，工作量 1200、耐久 600；16 份 → 16 堆（尸体一堆），内部固定 4℃正常推进腐烂 → 按确认规则落地。
+AI贴图占位：1.7/Textures/Things/Building/NingshaRace/DesertPit/AntColony/StoragePit.png</t>
+        </is>
       </c>
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
@@ -7254,12 +7461,16 @@
       <c r="S21" s="8"/>
       <c r="T21" s="8"/>
     </row>
-    <row r="22" s="6" customFormat="1" ht="241.5" spans="1:20">
+    <row r="22" s="6" customFormat="1" ht="241.5" spans="1:20" customHeight="1">
       <c r="A22" s="11" t="s">
         <v>107</v>
       </c>
       <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D22" s="11" t="s">
         <v>111</v>
       </c>
@@ -7267,8 +7478,12 @@
         <v>112</v>
       </c>
       <c r="F22" s="11"/>
-      <c r="G22" s="11" t="s">
-        <v>110</v>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暂无贴图可用任意原版贴图暂时占位
+30 任意石材 → 2 个可混用原石块，工作量 400、耐久 400 → 按确认规则；共用喷酸弹丸/射程/蓄力/冷却和原版距离命中率。
+AI贴图占位：1.7/Textures/Things/Building/NingshaRace/DesertPit/AntColony/AcidTurret.png</t>
+        </is>
       </c>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -7284,12 +7499,16 @@
       <c r="S22" s="11"/>
       <c r="T22" s="11"/>
     </row>
-    <row r="23" ht="409.5" spans="1:20">
+    <row r="23" ht="409.5" spans="1:20" customHeight="1">
       <c r="A23" s="8" t="s">
         <v>107</v>
       </c>
       <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D23" s="8" t="s">
         <v>113</v>
       </c>
@@ -7297,8 +7516,11 @@
         <v>114</v>
       </c>
       <c r="F23" s="8"/>
-      <c r="G23" s="8" t="s">
-        <v>110</v>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暂无贴图可用任意原版贴图暂时占位
+50 任意石材 → 3 个可混用原石块，工作量 1200、耐久 600 → 按确认规则；复用原共生菌巢素材。每塔独立产出，75 满停；初始目标 7～16 菌，受合法空地限制，5000 tick 补生，重叠生长取最高 2 倍。</t>
+        </is>
       </c>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
@@ -7314,12 +7536,16 @@
       <c r="S23" s="8"/>
       <c r="T23" s="8"/>
     </row>
-    <row r="24" s="6" customFormat="1" ht="34.5" spans="1:20">
+    <row r="24" s="6" customFormat="1" ht="154" spans="1:20" customHeight="1">
       <c r="A24" s="11" t="s">
         <v>115</v>
       </c>
       <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D24" s="11" t="s">
         <v>116</v>
       </c>
@@ -7327,8 +7553,12 @@
         <v>117</v>
       </c>
       <c r="F24" s="11"/>
-      <c r="G24" s="11" t="s">
-        <v>110</v>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暂无贴图可用任意原版贴图暂时占位
+美术表金色红纹 → 程序表绿色金纹 → 按已确认颜色；0.3 营养、心情 +3、腐烂 16 天。
+AI贴图占位：1.7/Textures/Things/Item/NingshaRace/AntColony/EmeraldHoneydew/EmeraldHoneydew_{a,b}.png（单件/堆叠）</t>
+        </is>
       </c>
       <c r="H24" s="11"/>
       <c r="I24" s="11"/>
@@ -7344,12 +7574,16 @@
       <c r="S24" s="11"/>
       <c r="T24" s="11"/>
     </row>
-    <row r="25" ht="34.5" spans="1:20">
+    <row r="25" ht="154" spans="1:20" customHeight="1">
       <c r="A25" s="8" t="s">
         <v>115</v>
       </c>
       <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D25" s="8" t="s">
         <v>118</v>
       </c>
@@ -7357,8 +7591,12 @@
         <v>119</v>
       </c>
       <c r="F25" s="8"/>
-      <c r="G25" s="8" t="s">
-        <v>110</v>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暂无贴图可用任意原版贴图暂时占位
+美术表绿色金纹 → 程序表金色红纹 → 按已确认颜色；0.4 营养、心情 +3、腐烂 16 天。
+AI贴图占位：1.7/Textures/Things/Item/NingshaRace/AntColony/BurstHoneydew/BurstHoneydew_{a,b}.png（单件/堆叠）</t>
+        </is>
       </c>
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
@@ -7374,12 +7612,16 @@
       <c r="S25" s="8"/>
       <c r="T25" s="8"/>
     </row>
-    <row r="26" s="6" customFormat="1" ht="27.4" customHeight="1" spans="1:20">
+    <row r="26" s="6" customFormat="1" ht="136" customHeight="1" spans="1:20">
       <c r="A26" s="11" t="s">
         <v>115</v>
       </c>
       <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D26" s="11" t="s">
         <v>120</v>
       </c>
@@ -7387,8 +7629,12 @@
         <v>121</v>
       </c>
       <c r="F26" s="11"/>
-      <c r="G26" s="11" t="s">
-        <v>110</v>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暂无贴图可用任意原版贴图暂时占位
+黑甲壳基础与材质数值暂同钢铁，独立资源 Def。
+AI贴图占位：1.7/Textures/Things/Item/NingshaRace/AntColony/BlackCarapace/BlackCarapace_{a,b}.png（单件/堆叠）</t>
+        </is>
       </c>
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
@@ -7404,12 +7650,16 @@
       <c r="S26" s="11"/>
       <c r="T26" s="11"/>
     </row>
-    <row r="27" spans="1:20">
+    <row r="27" spans="1:20" ht="172" customHeight="1">
       <c r="A27" s="8" t="s">
         <v>122</v>
       </c>
       <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D27" s="8" t="s">
         <v>123</v>
       </c>
@@ -7417,7 +7667,13 @@
         <v>124</v>
       </c>
       <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧共生菌巢 → 删除 1.7 定义、生成、采菇和旧收获加成，蜜露塔接替 → 只保留一套系统。
+地面仅占位 → 按用户追加要求实际铺满巢区/储藏/附属建筑，不规则外缘接原版 FadeRough；自写 GLSL 蠕动/脉动，暂停停止 → 蚁巢地面需呈现活体感。三地图共用。
+AI贴图占位：1.7/Textures/Terrain/Surfaces/NingshaRace/AntGround.png；Shader：1.7/Shaders/NingshaAntGround.frag.glsl</t>
+        </is>
+      </c>
       <c r="H27" s="8"/>
       <c r="I27" s="8"/>
       <c r="J27" s="8"/>
@@ -7432,12 +7688,16 @@
       <c r="S27" s="8"/>
       <c r="T27" s="8"/>
     </row>
-    <row r="28" s="6" customFormat="1" ht="34.5" spans="1:20">
+    <row r="28" s="6" customFormat="1" ht="64" spans="1:20" customHeight="1">
       <c r="A28" s="11" t="s">
         <v>125</v>
       </c>
       <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D28" s="11" t="s">
         <v>126</v>
       </c>
@@ -7445,7 +7705,11 @@
         <v>127</v>
       </c>
       <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一个蚂蚁种族 → 共用父 Def、成员组件、行为树，各蚁种保留独立属性/身体/贴图 → 复用行为且保留差异。</t>
+        </is>
+      </c>
       <c r="H28" s="11"/>
       <c r="I28" s="11"/>
       <c r="J28" s="11"/>
@@ -7460,12 +7724,16 @@
       <c r="S28" s="11"/>
       <c r="T28" s="11"/>
     </row>
-    <row r="29" spans="1:20">
+    <row r="29" spans="1:20" ht="64" customHeight="1">
       <c r="A29" s="8" t="s">
         <v>125</v>
       </c>
       <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D29" s="8" t="s">
         <v>128</v>
       </c>
@@ -7473,7 +7741,11 @@
         <v>129</v>
       </c>
       <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">普通孵化沿用 600 tick 工作、2500 tick 冷却；费用工 1/飞镰 1/兵 1.5/破军 3/吐酸 2；只执行巢群任务，完成再扣款。</t>
+        </is>
+      </c>
       <c r="H29" s="8"/>
       <c r="I29" s="8"/>
       <c r="J29" s="8"/>
@@ -7488,12 +7760,16 @@
       <c r="S29" s="8"/>
       <c r="T29" s="8"/>
     </row>
-    <row r="30" s="6" customFormat="1" ht="51.75" spans="1:20">
+    <row r="30" s="6" customFormat="1" ht="64" spans="1:20" customHeight="1">
       <c r="A30" s="11" t="s">
         <v>125</v>
       </c>
       <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D30" s="11" t="s">
         <v>130</v>
       </c>
@@ -7501,7 +7777,11 @@
         <v>131</v>
       </c>
       <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">按 30% 食物阈值，在当前工作结束后选择进食；地面储藏→储物穴→蜜露塔→地图物资，原版取食与营养更新。</t>
+        </is>
+      </c>
       <c r="H30" s="11"/>
       <c r="I30" s="11"/>
       <c r="J30" s="11"/>
@@ -7516,12 +7796,16 @@
       <c r="S30" s="11"/>
       <c r="T30" s="11"/>
     </row>
-    <row r="31" spans="1:20">
+    <row r="31" spans="1:20" ht="46" customHeight="1">
       <c r="A31" s="8" t="s">
         <v>125</v>
       </c>
       <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D31" s="8" t="s">
         <v>132</v>
       </c>
@@ -7529,7 +7813,11 @@
         <v>133</v>
       </c>
       <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工蚁、蚁后空闲时在巢周 9 格内闲逛；共享选址和行为。</t>
+        </is>
+      </c>
       <c r="H31" s="8"/>
       <c r="I31" s="8"/>
       <c r="J31" s="8"/>
@@ -7544,12 +7832,16 @@
       <c r="S31" s="8"/>
       <c r="T31" s="8"/>
     </row>
-    <row r="32" s="6" customFormat="1" spans="1:20">
+    <row r="32" s="6" customFormat="1" spans="1:20" ht="46" customHeight="1">
       <c r="A32" s="11" t="s">
         <v>125</v>
       </c>
       <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D32" s="11" t="s">
         <v>134</v>
       </c>
@@ -7557,7 +7849,11 @@
         <v>135</v>
       </c>
       <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">疲劳低于 20% 时在巢周 7 格内选择可达落点休息。</t>
+        </is>
+      </c>
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
       <c r="J32" s="11"/>
@@ -7572,12 +7868,16 @@
       <c r="S32" s="11"/>
       <c r="T32" s="11"/>
     </row>
-    <row r="33" spans="1:20">
+    <row r="33" spans="1:20" ht="46" customHeight="1">
       <c r="A33" s="8" t="s">
         <v>125</v>
       </c>
       <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D33" s="8" t="s">
         <v>136</v>
       </c>
@@ -7585,7 +7885,11 @@
         <v>137</v>
       </c>
       <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工蚁、蚁后检查自身 8 格内敌人并中断工作返巢，远处搬运也执行此检查。</t>
+        </is>
+      </c>
       <c r="H33" s="8"/>
       <c r="I33" s="8"/>
       <c r="J33" s="8"/>
@@ -7600,12 +7904,16 @@
       <c r="S33" s="8"/>
       <c r="T33" s="8"/>
     </row>
-    <row r="34" s="6" customFormat="1" ht="51.75" spans="1:20">
+    <row r="34" s="6" customFormat="1" ht="64" spans="1:20" customHeight="1">
       <c r="A34" s="11" t="s">
         <v>125</v>
       </c>
       <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D34" s="11" t="s">
         <v>138</v>
       </c>
@@ -7613,7 +7921,11 @@
         <v>139</v>
       </c>
       <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">按需求发掘 180 tick、半天冷却；原产出规则保留，发现物资后接续免费搬运，任务清理按身份释放。</t>
+        </is>
+      </c>
       <c r="H34" s="11"/>
       <c r="I34" s="11"/>
       <c r="J34" s="11"/>
@@ -7628,12 +7940,16 @@
       <c r="S34" s="11"/>
       <c r="T34" s="11"/>
     </row>
-    <row r="35" ht="51.75" spans="1:20">
+    <row r="35" ht="154" spans="1:20" customHeight="1">
       <c r="A35" s="8" t="s">
         <v>125</v>
       </c>
       <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D35" s="8" t="s">
         <v>140</v>
       </c>
@@ -7641,8 +7957,11 @@
         <v>141</v>
       </c>
       <c r="F35" s="8"/>
-      <c r="G35" s="8" t="s">
-        <v>142</v>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每只工蚁只会连续接取巢群派发的搬运任务5次，当累计五次后计数清零且 12游戏小时 内不再接收巢群的搬运任务，巢群也不会给它们派发；发掘后顺带的搬运不会计入次数
+按需求执行地面/建筑间实物搬运，成功五次后冷却 30000 tick，发掘接续不计额度；任务中断释放预留。</t>
+        </is>
       </c>
       <c r="H35" s="8"/>
       <c r="I35" s="8"/>
@@ -7658,12 +7977,16 @@
       <c r="S35" s="8"/>
       <c r="T35" s="8"/>
     </row>
-    <row r="36" s="6" customFormat="1" spans="1:20">
+    <row r="36" s="6" customFormat="1" spans="1:20" ht="82" customHeight="1">
       <c r="A36" s="11" t="s">
         <v>125</v>
       </c>
       <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D36" s="11" t="s">
         <v>143</v>
       </c>
@@ -7671,7 +7994,11 @@
         <v>144</v>
       </c>
       <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">按原版技能 6 工作参数施工；维修每 100 耐久 1 营养，受击等待 2500 tick。自动升级 → 工蚁施工 1200 工作量，10/50/100/500 营养、七天冷却 → 统一任务。</t>
+        </is>
+      </c>
       <c r="H36" s="11"/>
       <c r="I36" s="11"/>
       <c r="J36" s="11"/>
@@ -7686,12 +8013,16 @@
       <c r="S36" s="11"/>
       <c r="T36" s="11"/>
     </row>
-    <row r="37" ht="34.5" spans="1:20">
+    <row r="37" ht="64" spans="1:20" customHeight="1">
       <c r="A37" s="8" t="s">
         <v>125</v>
       </c>
       <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D37" s="8" t="s">
         <v>145</v>
       </c>
@@ -7699,7 +8030,11 @@
         <v>146</v>
       </c>
       <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">沿用通道破障选点，登记统一任务并独占目标；按六级采矿间隔及原版挖矿伤害、矿物末击产出。</t>
+        </is>
+      </c>
       <c r="H37" s="8"/>
       <c r="I37" s="8"/>
       <c r="J37" s="8"/>
@@ -7714,12 +8049,16 @@
       <c r="S37" s="8"/>
       <c r="T37" s="8"/>
     </row>
-    <row r="38" s="6" customFormat="1" ht="34.5" spans="1:20">
+    <row r="38" s="6" customFormat="1" ht="46" spans="1:20" customHeight="1">
       <c r="A38" s="11" t="s">
         <v>125</v>
       </c>
       <c r="B38" s="11"/>
-      <c r="C38" s="11"/>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D38" s="11" t="s">
         <v>147</v>
       </c>
@@ -7727,7 +8066,11 @@
         <v>148</v>
       </c>
       <c r="F38" s="11"/>
-      <c r="G38" s="11"/>
+      <c r="G38" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">按 12 格巡逻、20 格入侵缓存执行；目标含外来 Pawn、敌巢与原版虫巢。</t>
+        </is>
+      </c>
       <c r="H38" s="11"/>
       <c r="I38" s="11"/>
       <c r="J38" s="11"/>
@@ -7742,12 +8085,16 @@
       <c r="S38" s="11"/>
       <c r="T38" s="11"/>
     </row>
-    <row r="39" spans="1:20">
+    <row r="39" spans="1:20" ht="46" customHeight="1">
       <c r="A39" s="8" t="s">
         <v>125</v>
       </c>
       <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D39" s="8" t="s">
         <v>149</v>
       </c>
@@ -7755,7 +8102,11 @@
         <v>150</v>
       </c>
       <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">共用战斗调度；工/兵/蚁后近战、吐酸喷酸、破军冲锋、飞镰腾跃、爆浆自爆。</t>
+        </is>
+      </c>
       <c r="H39" s="8"/>
       <c r="I39" s="8"/>
       <c r="J39" s="8"/>
@@ -7770,12 +8121,16 @@
       <c r="S39" s="8"/>
       <c r="T39" s="8"/>
     </row>
-    <row r="40" s="6" customFormat="1" spans="1:20">
+    <row r="40" s="6" customFormat="1" spans="1:20" ht="46" customHeight="1">
       <c r="A40" s="11" t="s">
         <v>125</v>
       </c>
       <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D40" s="11" t="s">
         <v>151</v>
       </c>
@@ -7783,7 +8138,11 @@
         <v>152</v>
       </c>
       <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">非撤退时优先遇敌；远征队使用身边 20 格目标，冲锋/腾跃开始后不被反复重派。</t>
+        </is>
+      </c>
       <c r="H40" s="11"/>
       <c r="I40" s="11"/>
       <c r="J40" s="11"/>
@@ -7798,12 +8157,16 @@
       <c r="S40" s="11"/>
       <c r="T40" s="11"/>
     </row>
-    <row r="41" ht="51.75" spans="1:20">
+    <row r="41" ht="51.75" spans="1:20" customHeight="1">
       <c r="A41" s="8" t="s">
         <v>125</v>
       </c>
       <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D41" s="8" t="s">
         <v>153</v>
       </c>
@@ -7811,7 +8174,11 @@
         <v>154</v>
       </c>
       <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">调查队加入破军蚁；集结、往返使用兵蚁移动速度，抵达恢复各自速度。</t>
+        </is>
+      </c>
       <c r="H41" s="8"/>
       <c r="I41" s="8"/>
       <c r="J41" s="8"/>
@@ -7826,12 +8193,16 @@
       <c r="S41" s="8"/>
       <c r="T41" s="8"/>
     </row>
-    <row r="42" s="6" customFormat="1" ht="69" spans="1:20">
+    <row r="42" s="6" customFormat="1" ht="69" spans="1:20" customHeight="1">
       <c r="A42" s="11" t="s">
         <v>125</v>
       </c>
       <c r="B42" s="11"/>
-      <c r="C42" s="11"/>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D42" s="11" t="s">
         <v>155</v>
       </c>
@@ -7839,7 +8210,11 @@
         <v>156</v>
       </c>
       <c r="F42" s="11"/>
-      <c r="G42" s="11"/>
+      <c r="G42" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">按需求复仇 4500 tick 后返巢，往返兵蚁速度；警报、撤退会打断并释放领主。</t>
+        </is>
+      </c>
       <c r="H42" s="11"/>
       <c r="I42" s="11"/>
       <c r="J42" s="11"/>
@@ -7854,12 +8229,16 @@
       <c r="S42" s="11"/>
       <c r="T42" s="11"/>
     </row>
-    <row r="43" ht="34.5" spans="1:20">
+    <row r="43" ht="46" spans="1:20" customHeight="1">
       <c r="A43" s="8" t="s">
         <v>125</v>
       </c>
       <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D43" s="8" t="s">
         <v>157</v>
       </c>
@@ -7867,7 +8246,11 @@
         <v>158</v>
       </c>
       <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">撤退防御巢周 15 格可见敌人；记住实际攻击者、追击最多 45 格，失效后返巢。</t>
+        </is>
+      </c>
       <c r="H43" s="8"/>
       <c r="I43" s="8"/>
       <c r="J43" s="8"/>
@@ -7882,12 +8265,16 @@
       <c r="S43" s="8"/>
       <c r="T43" s="8"/>
     </row>
-    <row r="44" s="6" customFormat="1" ht="34.5" spans="1:20">
+    <row r="44" s="6" customFormat="1" ht="46" spans="1:20" customHeight="1">
       <c r="A44" s="11" t="s">
         <v>125</v>
       </c>
       <c r="B44" s="11"/>
-      <c r="C44" s="11"/>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D44" s="11" t="s">
         <v>159</v>
       </c>
@@ -7895,7 +8282,11 @@
         <v>160</v>
       </c>
       <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">巢内保存原 Pawn 唯一实例并暂停更新，不重新生成；存档保存容器，巢毁释放。</t>
+        </is>
+      </c>
       <c r="H44" s="11"/>
       <c r="I44" s="11"/>
       <c r="J44" s="11"/>
@@ -7910,12 +8301,16 @@
       <c r="S44" s="11"/>
       <c r="T44" s="11"/>
     </row>
-    <row r="45" ht="51.75" spans="1:20">
+    <row r="45" ht="64" spans="1:20" customHeight="1">
       <c r="A45" s="8" t="s">
         <v>125</v>
       </c>
       <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D45" s="8" t="s">
         <v>161</v>
       </c>
@@ -7923,7 +8318,11 @@
         <v>162</v>
       </c>
       <c r="F45" s="8"/>
-      <c r="G45" s="8"/>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">接敌或死亡单次爆炸，半径 2.5、25 AcidBurn、同巢免伤；销毁尸体并掉 3 爆浆蜜露。</t>
+        </is>
+      </c>
       <c r="H45" s="8"/>
       <c r="I45" s="8"/>
       <c r="J45" s="8"/>
@@ -7938,12 +8337,16 @@
       <c r="S45" s="8"/>
       <c r="T45" s="8"/>
     </row>
-    <row r="46" s="6" customFormat="1" ht="51.75" spans="1:20">
+    <row r="46" s="6" customFormat="1" ht="64" spans="1:20" customHeight="1">
       <c r="A46" s="11" t="s">
         <v>163</v>
       </c>
       <c r="B46" s="11"/>
-      <c r="C46" s="11"/>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D46" s="11" t="s">
         <v>164</v>
       </c>
@@ -7951,7 +8354,11 @@
         <v>165</v>
       </c>
       <c r="F46" s="11"/>
-      <c r="G46" s="11"/>
+      <c r="G46" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">蚁后独立保存，普通需求/躲避/孵化共享行为；警报时入巢暂停需求和孵化。甲壳未定 → 暂定 8 → 按确认补充值。</t>
+        </is>
+      </c>
       <c r="H46" s="11"/>
       <c r="I46" s="11"/>
       <c r="J46" s="11"/>
@@ -7966,12 +8373,16 @@
       <c r="S46" s="11"/>
       <c r="T46" s="11"/>
     </row>
-    <row r="47" ht="103.5" spans="1:20">
+    <row r="47" ht="103.5" spans="1:20" customHeight="1">
       <c r="A47" s="8" t="s">
         <v>163</v>
       </c>
       <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D47" s="8" t="s">
         <v>166</v>
       </c>
@@ -7979,7 +8390,11 @@
         <v>167</v>
       </c>
       <c r="F47" s="8"/>
-      <c r="G47" s="12"/>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工蚁上限 4×等级，孵化 1 营养、屠宰 2 黑甲壳；搬运、发掘、建造、维修、破障使用统一任务。</t>
+        </is>
+      </c>
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
       <c r="J47" s="8"/>
@@ -7994,12 +8409,16 @@
       <c r="S47" s="8"/>
       <c r="T47" s="8"/>
     </row>
-    <row r="48" s="6" customFormat="1" ht="103.5" spans="1:20">
+    <row r="48" s="6" customFormat="1" ht="103.5" spans="1:20" customHeight="1">
       <c r="A48" s="11" t="s">
         <v>163</v>
       </c>
       <c r="B48" s="11"/>
-      <c r="C48" s="11"/>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D48" s="11" t="s">
         <v>168</v>
       </c>
@@ -8007,7 +8426,11 @@
         <v>169</v>
       </c>
       <c r="F48" s="11"/>
-      <c r="G48" s="11"/>
+      <c r="G48" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">兵蚁上限 3×等级，孵化 1.5 营养、屠宰 3 黑甲壳；属性保持原基准，使用共用行为。</t>
+        </is>
+      </c>
       <c r="H48" s="11"/>
       <c r="I48" s="11"/>
       <c r="J48" s="11"/>
@@ -8022,12 +8445,16 @@
       <c r="S48" s="11"/>
       <c r="T48" s="11"/>
     </row>
-    <row r="49" ht="172.5" spans="1:20">
+    <row r="49" ht="172.5" spans="1:20" customHeight="1">
       <c r="A49" s="8" t="s">
         <v>163</v>
       </c>
       <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D49" s="8" t="s">
         <v>170</v>
       </c>
@@ -8035,7 +8462,11 @@
         <v>171</v>
       </c>
       <c r="F49" s="8"/>
-      <c r="G49" s="8"/>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">冲锋写在吐酸蚁/上限名写为破军 → 冲锋归破军，吐酸保留喷酸；两种上限均 max(0,等级−2)×2 → 按确认消除表格冲突。孵化 2 营养、甲壳 3。</t>
+        </is>
+      </c>
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
       <c r="J49" s="8"/>
@@ -8050,12 +8481,16 @@
       <c r="S49" s="8"/>
       <c r="T49" s="8"/>
     </row>
-    <row r="50" s="6" customFormat="1" ht="120.75" spans="1:20">
+    <row r="50" s="6" customFormat="1" ht="409" spans="1:20" customHeight="1">
       <c r="A50" s="11" t="s">
         <v>163</v>
       </c>
       <c r="B50" s="11"/>
-      <c r="C50" s="11"/>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D50" s="11" t="s">
         <v>172</v>
       </c>
@@ -8063,7 +8498,15 @@
         <v>173</v>
       </c>
       <c r="F50" s="11"/>
-      <c r="G50" s="11"/>
+      <c r="G50" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">其余属性 1.5 倍 → 体型/生命/护甲/伤害/饥饿 1.5 倍，速度及攻击间隔同兵蚁；孵化 3 营养 → 按确认具体化。冲锋蓄力 180 tick、9 格、1.5 倍移速、40 钝击推 2 格、冷却 20000；沿途同巢也受伤，每实体一次，碰墙停。
+AI贴图占位：1.7/Textures/Things/Pawn/Animal/NingshaRace/DesertPit/AntColony/BreakerAnt/BreakerAnt_{south,north,east}.png
+2026-10-31 冲锋补充：仅有冲锋数值、无明显预警 → 当前战斗目标不限种类，近身也可触发，敌建筑可在边缘受撞击；增加方向箭头、蓄力进度、扬尘及命中短闪；实际起冲才扣冷却，普通受击换目标不打断 → 按用户要求补强表现，修复蓄力取消仍扣冷却。原数值不变。
+2026-10-31 冲锋表现与执行：移速 1.5 倍、线条箭头、警报/撤退可取消 → 移速 4 倍，红色半透明连续范围、细边框、方向箭头及蓄力填充，起冲环形闪光、扬尘、速度拖尾与平滑移动；触发后锁定落点，换目标、目标死亡/离开、警报、撤退及巢毁不取消，被推开后继续朝锁定落点冲出；死亡、倒地、离图和撞墙正常处理 → 按用户要求提高速度和范围辨识度，保证动作执行。
+追加：4倍匀速/自绘 → 3秒前摇、0.75秒加速至2倍，撞墙40钝击＋1秒僵直特效；原版红边复用路线、仅蓄力可见，跳跃不画 → 按反馈调整节奏与性能。</t>
+        </is>
+      </c>
       <c r="H50" s="11"/>
       <c r="I50" s="11"/>
       <c r="J50" s="11"/>
@@ -8078,12 +8521,16 @@
       <c r="S50" s="11"/>
       <c r="T50" s="11"/>
     </row>
-    <row r="51" s="6" customFormat="1" ht="189.75" spans="1:20">
+    <row r="51" s="6" customFormat="1" ht="300" spans="1:20" customHeight="1">
       <c r="A51" s="11" t="s">
         <v>163</v>
       </c>
       <c r="B51" s="11"/>
-      <c r="C51" s="11"/>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D51" s="11" t="s">
         <v>174</v>
       </c>
@@ -8091,7 +8538,13 @@
         <v>175</v>
       </c>
       <c r="F51" s="11"/>
-      <c r="G51" s="11"/>
+      <c r="G51" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻击能力 1.8 倍 → 单次伤害和速度 1.8 倍，攻击间隔同兵蚁；体型/生命/护甲/饥饿 0.7 倍，孵化 1 营养 → 按确认具体化。原版腾跃 7 格、冷却 15000，检查落点不入墙。
+AI贴图占位：1.7/Textures/Things/Pawn/Animal/NingshaRace/DesertPit/AntColony/FlyingAnt/FlyingAnt_{south,north,east}.png
+2026-10-31 腾跃执行：原版飞行器会挂起并在落地恢复自定义跳跃任务，绕过派活冷却反复起跳 → 起跳前结束任务再创建飞行器，执行入口也检查 15000 tick 冷却；已触发动作不被换目标、警报、撤退或巢毁中断 → 修复攻击震尼时连续重跳，并按用户要求保证动作执行。</t>
+        </is>
+      </c>
       <c r="H51" s="11"/>
       <c r="I51" s="11"/>
       <c r="J51" s="11"/>
@@ -8106,12 +8559,16 @@
       <c r="S51" s="11"/>
       <c r="T51" s="11"/>
     </row>
-    <row r="52" ht="120.75" spans="1:20">
+    <row r="52" ht="120.75" spans="1:20" customHeight="1">
       <c r="A52" s="8" t="s">
         <v>163</v>
       </c>
       <c r="B52" s="8"/>
-      <c r="C52" s="8"/>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D52" s="8" t="s">
         <v>176</v>
       </c>
@@ -8119,7 +8576,11 @@
         <v>177</v>
       </c>
       <c r="F52" s="8"/>
-      <c r="G52" s="8"/>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">固定上限 3（含休眠），20 格入侵或警报时出巢，安静后返回；1200 tick 补齐，不走蚁后孵化。</t>
+        </is>
+      </c>
       <c r="H52" s="8"/>
       <c r="I52" s="8"/>
       <c r="J52" s="8"/>
@@ -8134,12 +8595,16 @@
       <c r="S52" s="8"/>
       <c r="T52" s="8"/>
     </row>
-    <row r="53" s="6" customFormat="1" ht="34.5" spans="1:20">
+    <row r="53" s="6" customFormat="1" ht="64" spans="1:20" customHeight="1">
       <c r="A53" s="11" t="s">
         <v>163</v>
       </c>
       <c r="B53" s="11"/>
-      <c r="C53" s="11"/>
+      <c r="C53" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
       <c r="D53" s="11" t="s">
         <v>178</v>
       </c>
@@ -8147,7 +8612,11 @@
         <v>179</v>
       </c>
       <c r="F53" s="11"/>
-      <c r="G53" s="11"/>
+      <c r="G53" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">按需求普通蚂蚁尸体屠宰产肉+甲壳，风干后删除尸体并仅产等量甲壳；爆浆沿用不留尸体专属规则。</t>
+        </is>
+      </c>
       <c r="H53" s="11"/>
       <c r="I53" s="11"/>
       <c r="J53" s="11"/>
@@ -12188,7 +12657,7 @@
     <col min="6" max="7" width="16.1666666666667" style="1" customWidth="1"/>
     <col min="8" max="8" width="21.8" style="1" customWidth="1"/>
     <col min="9" max="9" width="18.7666666666667" style="1" customWidth="1"/>
-    <col min="10" max="10" width="16.4" style="1" customWidth="1"/>
+    <col min="10" max="10" width="60" style="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -12258,7 +12727,7 @@
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
     </row>
-    <row r="3" ht="57.15" customHeight="1" spans="1:21">
+    <row r="3" ht="100" customHeight="1" spans="1:21">
       <c r="A3" s="2" t="s">
         <v>116</v>
       </c>
@@ -12274,7 +12743,12 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">美术表金色红纹 → 程序表绿色金纹 → 按已确认颜色；0.3 营养、心情 +3、腐烂 16 天。
+AI贴图占位：1.7/Textures/Things/Item/NingshaRace/AntColony/EmeraldHoneydew/EmeraldHoneydew_{a,b}.png（单件/堆叠）</t>
+        </is>
+      </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
@@ -12287,7 +12761,7 @@
       <c r="T3" s="2"/>
       <c r="U3" s="2"/>
     </row>
-    <row r="4" ht="57.15" customHeight="1" spans="1:21">
+    <row r="4" ht="82" customHeight="1" spans="1:21">
       <c r="A4" s="2" t="s">
         <v>118</v>
       </c>
@@ -12303,7 +12777,12 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">美术表绿色金纹 → 程序表金色红纹 → 按已确认颜色；0.4 营养、心情 +3、腐烂 16 天。
+AI贴图占位：1.7/Textures/Things/Item/NingshaRace/AntColony/BurstHoneydew/BurstHoneydew_{a,b}.png（单件/堆叠）</t>
+        </is>
+      </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
@@ -12316,7 +12795,7 @@
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
     </row>
-    <row r="5" ht="57.15" customHeight="1" spans="1:21">
+    <row r="5" ht="64" customHeight="1" spans="1:21">
       <c r="A5" s="2" t="s">
         <v>120</v>
       </c>
@@ -12332,7 +12811,12 @@
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI贴图占位，正式美术未完成。
+1.7/Textures/Things/Item/NingshaRace/AntColony/BlackCarapace/BlackCarapace_{a,b}.png（单件/堆叠）</t>
+        </is>
+      </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
@@ -12345,7 +12829,7 @@
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
     </row>
-    <row r="6" ht="57.15" customHeight="1" spans="1:21">
+    <row r="6" ht="100" customHeight="1" spans="1:21">
       <c r="A6" s="2" t="s">
         <v>185</v>
       </c>
@@ -12361,7 +12845,12 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仅地面占位 → 用户追加为实际铺设巢区，外缘不规则，接原版 FadeRough 与 GLSL 活体蠕动 → 满足追加要求。参考原版地板格式，1024×1024 整张不透明平铺。
+AI贴图占位：1.7/Textures/Terrain/Surfaces/NingshaRace/AntGround.png</t>
+        </is>
+      </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
@@ -12374,7 +12863,7 @@
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
     </row>
-    <row r="7" ht="57.15" customHeight="1" spans="1:21">
+    <row r="7" ht="64" customHeight="1" spans="1:21">
       <c r="A7" s="2" t="s">
         <v>188</v>
       </c>
@@ -12390,7 +12879,12 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI贴图占位，正式美术未完成。
+1.7/Textures/Things/Building/NingshaRace/DesertPit/AntColony/StoragePit.png</t>
+        </is>
+      </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
@@ -12403,7 +12897,7 @@
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
     </row>
-    <row r="8" ht="57.15" customHeight="1" spans="1:21">
+    <row r="8" ht="64" customHeight="1" spans="1:21">
       <c r="A8" s="2" t="s">
         <v>191</v>
       </c>
@@ -12419,7 +12913,12 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI贴图占位，正式美术未完成。
+1.7/Textures/Things/Building/NingshaRace/DesertPit/AntColony/AcidTurret.png</t>
+        </is>
+      </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
@@ -12432,7 +12931,7 @@
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
     </row>
-    <row r="9" ht="57.15" customHeight="1" spans="1:21">
+    <row r="9" ht="64" customHeight="1" spans="1:21">
       <c r="A9" s="2" t="s">
         <v>172</v>
       </c>
@@ -12448,7 +12947,12 @@
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI贴图占位，南/北/东三向，正式美术未完成。
+1.7/Textures/Things/Pawn/Animal/NingshaRace/DesertPit/AntColony/BreakerAnt/BreakerAnt_{south,north,east}.png</t>
+        </is>
+      </c>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
@@ -12461,7 +12965,7 @@
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
     </row>
-    <row r="10" ht="57.15" customHeight="1" spans="1:21">
+    <row r="10" ht="64" customHeight="1" spans="1:21">
       <c r="A10" s="2" t="s">
         <v>174</v>
       </c>
@@ -12477,7 +12981,12 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI贴图占位，南/北/东三向，正式美术未完成。
+1.7/Textures/Things/Pawn/Animal/NingshaRace/DesertPit/AntColony/FlyingAnt/FlyingAnt_{south,north,east}.png</t>
+        </is>
+      </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
